--- a/data/인천광역시/미추홀도서관.xlsx
+++ b/data/인천광역시/미추홀도서관.xlsx
@@ -7,11 +7,11 @@
   </bookViews>
   <sheets>
     <sheet name="입력" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="인천광역시교육청서구도서관" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="인천광역시교육청평생학습관" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="인천광역시교육청부평도서관" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="인천광역시교육청중앙도서관" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="인천광역시교육청화도진도서관" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="인천광역시교육청평생학습관" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="인천광역시교육청서구도서관" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="인천광역시교육청중앙도서관" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="인천광역시교육청화도진도서관" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="인천광역시교육청계양도서관" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -458,6 +458,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="652" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코. 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843-이민진파1-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[평생]어린이자료실 청구기호 : 843-이민진파1-2 등록번호 : PEJ000012778    도서 상태 및 등록 정보          대출가능여부 반납예정일 상호대차  야간대출예약 예약가능여부     
+ 																	대출가능
+ 														-
+ 												   상호대차신청    
+ 															예약불가(0/2)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -635,157 +710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="652" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843-이민진파1-2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[평생]어린이자료실 청구기호 : 843-이민진파1-2 등록번호 : PEJ000012778    도서 상태 및 등록 정보          대출가능여부 반납예정일 상호대차  야간대출예약 예약가능여부     
- 																	대출가능
- 														-
- 												   상호대차신청    
- 															예약불가(0/2)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="658" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843-이39ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음  ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[부평]종합자료실 청구기호 : 843-이39ㅍ-2 등록번호 : EMC000249232    도서 상태 및 등록 정보          대출가능여부 반납예정일 상호대차  야간대출예약 예약가능여부     
- 																	대출가능
- 														-
- 												   상호대차신청     신청하기  
- 															예약불가(0/2)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -887,7 +812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -960,4 +885,79 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="664" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843-이민진파2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[계양]종합자료실(2층) 청구기호 : 843-이민진파2 등록번호 : EME000218436    도서 상태 및 등록 정보          대출가능여부 반납예정일 상호대차  야간대출예약 예약가능여부     
+ 																	대출가능
+ 														-
+ 												   상호대차신청     신청하기  
+ 															예약불가(0/2)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>